--- a/MG-Hote-ERP/MG_Hote_Gestion_Conciergerie.xlsx
+++ b/MG-Hote-ERP/MG_Hote_Gestion_Conciergerie.xlsx
@@ -2066,11 +2066,11 @@
     <row r="17">
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Revenu locatif encaissé</t>
+          <t>Revenu locatif brut</t>
         </is>
       </c>
       <c r="C17" s="41">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Bien],$C$6,T_Finances[Mois],$F$6)</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Bien],$C$6,T_Reservations[Mois],$F$6,T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
     </row>
@@ -2271,11 +2271,11 @@
     <row r="8">
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Chiffre d'affaires total</t>
+          <t>Chiffre d'affaires brut total</t>
         </is>
       </c>
       <c r="C8" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],$C$4)</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],$C$4,T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
     </row>
@@ -2838,11 +2838,11 @@
     <row r="11">
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Chiffre d'affaires du mois</t>
+          <t>Chiffre d'affaires brut du mois</t>
         </is>
       </c>
       <c r="G11" s="19">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(TODAY(),"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(TODAY(),"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
         <v/>
       </c>
       <c r="C46" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B46,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B46,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D46" s="23">
@@ -3034,7 +3034,7 @@
         <v/>
       </c>
       <c r="C47" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B47,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B47,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D47" s="23">
@@ -3048,7 +3048,7 @@
         <v/>
       </c>
       <c r="C48" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B48,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B48,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D48" s="23">
@@ -3062,7 +3062,7 @@
         <v/>
       </c>
       <c r="C49" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B49,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B49,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D49" s="23">
@@ -3076,7 +3076,7 @@
         <v/>
       </c>
       <c r="C50" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B50,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B50,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D50" s="23">
@@ -3090,7 +3090,7 @@
         <v/>
       </c>
       <c r="C51" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B51,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B51,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D51" s="23">
@@ -3104,7 +3104,7 @@
         <v/>
       </c>
       <c r="C52" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B52,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B52,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D52" s="23">
@@ -3118,7 +3118,7 @@
         <v/>
       </c>
       <c r="C53" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B53,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B53,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D53" s="23">
@@ -3132,7 +3132,7 @@
         <v/>
       </c>
       <c r="C54" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B54,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B54,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D54" s="23">
@@ -3146,7 +3146,7 @@
         <v/>
       </c>
       <c r="C55" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B55,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B55,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D55" s="23">
@@ -3160,7 +3160,7 @@
         <v/>
       </c>
       <c r="C56" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B56,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B56,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D56" s="23">
@@ -3174,7 +3174,7 @@
         <v/>
       </c>
       <c r="C57" s="22">
-        <f>SUMIFS(T_Finances[Revenu locatif],T_Finances[Mois],TEXT(B57,"yyyy-mm"))</f>
+        <f>SUMIFS(T_Reservations[Prix total (TTC)],T_Reservations[Mois],TEXT(B57,"yyyy-mm"),T_Reservations[Statut],"&lt;&gt;Annulée")</f>
         <v/>
       </c>
       <c r="D57" s="23">
